--- a/data/Escenarios_DCH/Costo_variable/Swap_variable_3estaciones_530kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH/Costo_variable/Swap_variable_3estaciones_530kW/elmo_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agustin\Desktop\Elmo_infrastructure_NP\data\Escenarios_DCH\Costo_variable\Swap_variable_3estaciones_530kW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH\Costo_variable\Swap_variable_3estaciones_530kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881AD343-2680-4289-B770-05E971B43819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -2093,36 +2093,36 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:AE17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" style="23" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7" style="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" style="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15" style="23" customWidth="1"/>
-    <col min="16" max="16" width="17.109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.5703125" style="24" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="18" style="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.88671875" style="24" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="20.88671875" style="24" customWidth="1"/>
-    <col min="24" max="24" width="18.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="20.109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="20.85546875" style="24" customWidth="1"/>
+    <col min="24" max="24" width="18.42578125" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="20.140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="24" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31">
         <v>1</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31">
         <v>2</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="31">
         <v>3</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="31">
         <v>4</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="31">
         <v>5</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="31">
         <v>6</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>7</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>8</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
         <v>9</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>10</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>11</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" s="34" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>12</v>
       </c>
@@ -3461,9 +3461,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3473,13 +3473,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC93900-5A86-4519-AB89-460E8AC441EE}">
   <dimension ref="A1:H5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3618,12 +3618,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA5C58D2-31A1-4CA6-99E5-3102447D41CF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3675,7 +3675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3712,17 +3712,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:H346"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="51" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="29.109375" style="71" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="51" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="29.140625" style="71" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="53" t="s">
         <v>3</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="54">
         <v>0</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="55">
         <v>1</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="55">
         <v>2</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="54">
         <v>3</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="55">
         <v>4</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="55">
         <v>5</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="54">
         <v>6</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="55">
         <v>7</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="55">
         <v>8</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="54">
         <v>9</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="55">
         <v>10</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="55">
         <v>11</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="55">
         <v>12</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="54">
         <v>13</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55">
         <v>14</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
         <v>15</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54">
         <v>16</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
         <v>17</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55">
         <v>18</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54">
         <v>19</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="55">
         <v>20</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="55">
         <v>21</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="55">
         <v>22</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="54">
         <v>23</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="55">
         <v>24</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="54">
         <v>25</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="55">
         <v>26</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="55">
         <v>27</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54">
         <v>28</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="55">
         <v>29</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="55">
         <v>30</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="54">
         <v>31</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="55">
         <v>32</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="55">
         <v>33</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="54">
         <v>34</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="55">
         <v>35</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="55">
         <v>36</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="55">
         <v>37</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="54">
         <v>38</v>
       </c>
@@ -4788,7 +4788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="55">
         <v>39</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="55">
         <v>40</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="55">
         <v>41</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="55">
         <v>42</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="55">
         <v>43</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="55">
         <v>44</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="55">
         <v>45</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="55">
         <v>46</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="55">
         <v>47</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="55">
         <v>48</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="55">
         <v>49</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="55">
         <v>50</v>
       </c>
@@ -5100,7 +5100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="55">
         <v>51</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="55">
         <v>52</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="55">
         <v>53</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="55">
         <v>54</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="55">
         <v>55</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="55">
         <v>56</v>
       </c>
@@ -5256,7 +5256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="55">
         <v>57</v>
       </c>
@@ -5282,7 +5282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="55">
         <v>58</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="55">
         <v>59</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="55">
         <v>60</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="55">
         <v>61</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="55">
         <v>62</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="55">
         <v>63</v>
       </c>
@@ -5438,7 +5438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="55">
         <v>64</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="55">
         <v>65</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="55">
         <v>66</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="55">
         <v>67</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="55">
         <v>68</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="55">
         <v>69</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="55">
         <v>70</v>
       </c>
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="55">
         <v>71</v>
       </c>
@@ -5646,7 +5646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="55">
         <v>72</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="55">
         <v>73</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="55">
         <v>74</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="55">
         <v>75</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="55">
         <v>76</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="55">
         <v>77</v>
       </c>
@@ -5802,7 +5802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="55">
         <v>78</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="55">
         <v>79</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="55">
         <v>80</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="55">
         <v>81</v>
       </c>
@@ -5906,7 +5906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="55">
         <v>82</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="55">
         <v>83</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="55">
         <v>84</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="55">
         <v>85</v>
       </c>
@@ -6010,7 +6010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="55">
         <v>86</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="55">
         <v>87</v>
       </c>
@@ -6062,7 +6062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="55">
         <v>88</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="55">
         <v>89</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="55">
         <v>90</v>
       </c>
@@ -6140,7 +6140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="55">
         <v>91</v>
       </c>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="55">
         <v>92</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="55">
         <v>93</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="55">
         <v>94</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="55">
         <v>95</v>
       </c>
@@ -6270,7 +6270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="55">
         <v>96</v>
       </c>
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="55">
         <v>97</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="55">
         <v>98</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="55">
         <v>99</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="55">
         <v>100</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="55">
         <v>101</v>
       </c>
@@ -6426,7 +6426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="55">
         <v>102</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="55">
         <v>103</v>
       </c>
@@ -6478,7 +6478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="55">
         <v>104</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="55">
         <v>105</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="55">
         <v>106</v>
       </c>
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="55">
         <v>107</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="55">
         <v>108</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="55">
         <v>109</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="55">
         <v>110</v>
       </c>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="55">
         <v>111</v>
       </c>
@@ -6686,7 +6686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="55">
         <v>112</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="55">
         <v>113</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="55">
         <v>114</v>
       </c>
@@ -6764,7 +6764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="55">
         <v>115</v>
       </c>
@@ -6790,7 +6790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="55">
         <v>116</v>
       </c>
@@ -6816,7 +6816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="55">
         <v>117</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="55">
         <v>118</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="55">
         <v>119</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="55">
         <v>120</v>
       </c>
@@ -6920,7 +6920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="55">
         <v>121</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="55">
         <v>122</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="55">
         <v>123</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="55">
         <v>124</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="55">
         <v>125</v>
       </c>
@@ -7050,7 +7050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="55">
         <v>126</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="55">
         <v>127</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="55">
         <v>128</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="55">
         <v>129</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="55">
         <v>130</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="55">
         <v>131</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="55">
         <v>132</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="55">
         <v>133</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="55">
         <v>134</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="55">
         <v>135</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="55">
         <v>136</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="55">
         <v>137</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="55">
         <v>138</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="55">
         <v>139</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="55">
         <v>140</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="55">
         <v>141</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="55">
         <v>142</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="55">
         <v>143</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="55">
         <v>144</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="55">
         <v>145</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="55">
         <v>146</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="55">
         <v>147</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="55">
         <v>148</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="55">
         <v>149</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="55">
         <v>150</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="55">
         <v>151</v>
       </c>
@@ -7726,7 +7726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="55">
         <v>152</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="55">
         <v>153</v>
       </c>
@@ -7778,7 +7778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="55">
         <v>154</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="55">
         <v>155</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="55">
         <v>156</v>
       </c>
@@ -7856,7 +7856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="55">
         <v>157</v>
       </c>
@@ -7882,7 +7882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="55">
         <v>158</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="55">
         <v>159</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="55">
         <v>160</v>
       </c>
@@ -7960,7 +7960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="55">
         <v>161</v>
       </c>
@@ -7986,7 +7986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="55">
         <v>162</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="55">
         <v>163</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="55">
         <v>164</v>
       </c>
@@ -8064,7 +8064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="55">
         <v>165</v>
       </c>
@@ -8090,7 +8090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="55">
         <v>166</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="55">
         <v>167</v>
       </c>
@@ -8142,7 +8142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="55">
         <v>168</v>
       </c>
@@ -8168,7 +8168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="55">
         <v>169</v>
       </c>
@@ -8194,7 +8194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="55">
         <v>170</v>
       </c>
@@ -8220,7 +8220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="55">
         <v>171</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="55">
         <v>172</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="55">
         <v>173</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="55">
         <v>174</v>
       </c>
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="55">
         <v>175</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="55">
         <v>176</v>
       </c>
@@ -8376,7 +8376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="55">
         <v>177</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="55">
         <v>178</v>
       </c>
@@ -8428,7 +8428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="55">
         <v>179</v>
       </c>
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="55">
         <v>180</v>
       </c>
@@ -8480,7 +8480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="55">
         <v>181</v>
       </c>
@@ -8506,7 +8506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="55">
         <v>182</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="55">
         <v>183</v>
       </c>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="55">
         <v>184</v>
       </c>
@@ -8584,7 +8584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="55">
         <v>185</v>
       </c>
@@ -8610,7 +8610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="55">
         <v>186</v>
       </c>
@@ -8636,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="55">
         <v>187</v>
       </c>
@@ -8662,7 +8662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="55">
         <v>188</v>
       </c>
@@ -8688,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="55">
         <v>189</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="55">
         <v>190</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="55">
         <v>191</v>
       </c>
@@ -8766,7 +8766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="55">
         <v>192</v>
       </c>
@@ -8792,7 +8792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="55">
         <v>193</v>
       </c>
@@ -8818,7 +8818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="55">
         <v>194</v>
       </c>
@@ -8844,7 +8844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="55">
         <v>195</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="55">
         <v>196</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="55">
         <v>197</v>
       </c>
@@ -8922,7 +8922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="55">
         <v>198</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="55">
         <v>199</v>
       </c>
@@ -8974,7 +8974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="55">
         <v>200</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="55">
         <v>201</v>
       </c>
@@ -9026,7 +9026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="55">
         <v>202</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="55">
         <v>203</v>
       </c>
@@ -9078,7 +9078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="55">
         <v>204</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="55">
         <v>205</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="55">
         <v>206</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="55">
         <v>207</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="55">
         <v>208</v>
       </c>
@@ -9208,7 +9208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="55">
         <v>209</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="55">
         <v>210</v>
       </c>
@@ -9260,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="55">
         <v>211</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="55">
         <v>212</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="55">
         <v>213</v>
       </c>
@@ -9338,7 +9338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="55">
         <v>214</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="55">
         <v>215</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="55">
         <v>216</v>
       </c>
@@ -9416,7 +9416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="55">
         <v>217</v>
       </c>
@@ -9442,7 +9442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="55">
         <v>218</v>
       </c>
@@ -9468,7 +9468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="55">
         <v>219</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="55">
         <v>220</v>
       </c>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="55">
         <v>221</v>
       </c>
@@ -9546,7 +9546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="55">
         <v>222</v>
       </c>
@@ -9572,7 +9572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="55">
         <v>223</v>
       </c>
@@ -9598,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="55">
         <v>224</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="55">
         <v>225</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="55">
         <v>226</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="55">
         <v>227</v>
       </c>
@@ -9702,7 +9702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="55">
         <v>228</v>
       </c>
@@ -9728,7 +9728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="55">
         <v>229</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="55">
         <v>230</v>
       </c>
@@ -9780,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="55">
         <v>231</v>
       </c>
@@ -9806,7 +9806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="55">
         <v>232</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="55">
         <v>233</v>
       </c>
@@ -9858,7 +9858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="55">
         <v>234</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="55">
         <v>235</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="55">
         <v>236</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="55">
         <v>237</v>
       </c>
@@ -9962,7 +9962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="55">
         <v>238</v>
       </c>
@@ -9988,7 +9988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="55">
         <v>239</v>
       </c>
@@ -10014,7 +10014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="55">
         <v>240</v>
       </c>
@@ -10040,7 +10040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="55">
         <v>241</v>
       </c>
@@ -10066,7 +10066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="55">
         <v>242</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="55">
         <v>243</v>
       </c>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="55">
         <v>244</v>
       </c>
@@ -10144,7 +10144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="55">
         <v>245</v>
       </c>
@@ -10170,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="55">
         <v>246</v>
       </c>
@@ -10196,7 +10196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="55">
         <v>247</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="55">
         <v>248</v>
       </c>
@@ -10248,7 +10248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="55">
         <v>249</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="55">
         <v>250</v>
       </c>
@@ -10300,7 +10300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="55">
         <v>251</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="55">
         <v>252</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="55">
         <v>253</v>
       </c>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="55">
         <v>254</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="55">
         <v>255</v>
       </c>
@@ -10430,7 +10430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="55">
         <v>256</v>
       </c>
@@ -10456,7 +10456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="55">
         <v>257</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="55">
         <v>258</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="55">
         <v>259</v>
       </c>
@@ -10534,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="55">
         <v>260</v>
       </c>
@@ -10560,7 +10560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="55">
         <v>261</v>
       </c>
@@ -10586,7 +10586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="55">
         <v>262</v>
       </c>
@@ -10612,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="55">
         <v>263</v>
       </c>
@@ -10638,7 +10638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="55">
         <v>264</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="55">
         <v>265</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="55">
         <v>266</v>
       </c>
@@ -10716,7 +10716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="55">
         <v>267</v>
       </c>
@@ -10742,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="55">
         <v>268</v>
       </c>
@@ -10768,7 +10768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="55">
         <v>269</v>
       </c>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="55">
         <v>270</v>
       </c>
@@ -10820,7 +10820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="55">
         <v>271</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="55">
         <v>272</v>
       </c>
@@ -10872,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="55">
         <v>273</v>
       </c>
@@ -10898,7 +10898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="55">
         <v>274</v>
       </c>
@@ -10924,7 +10924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="55">
         <v>275</v>
       </c>
@@ -10950,7 +10950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="55">
         <v>276</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="55">
         <v>277</v>
       </c>
@@ -11002,7 +11002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="55">
         <v>278</v>
       </c>
@@ -11028,7 +11028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="55">
         <v>279</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="55">
         <v>280</v>
       </c>
@@ -11080,7 +11080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="55">
         <v>281</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="55">
         <v>282</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="55">
         <v>283</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="55">
         <v>284</v>
       </c>
@@ -11184,7 +11184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="55">
         <v>285</v>
       </c>
@@ -11210,7 +11210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="55">
         <v>286</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="55">
         <v>287</v>
       </c>
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="55"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="56"/>
       <c r="B292" s="66"/>
       <c r="C292" s="63"/>
@@ -11273,7 +11273,7 @@
       <c r="G292" s="43"/>
       <c r="H292" s="44"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="57"/>
       <c r="B293" s="66"/>
       <c r="C293" s="64"/>
@@ -11281,7 +11281,7 @@
       <c r="G293" s="37"/>
       <c r="H293" s="8"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="58"/>
       <c r="B294" s="66"/>
       <c r="C294" s="64"/>
@@ -11289,7 +11289,7 @@
       <c r="G294" s="37"/>
       <c r="H294" s="8"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="59"/>
       <c r="B295" s="66"/>
       <c r="C295" s="64"/>
@@ -11297,7 +11297,7 @@
       <c r="G295" s="37"/>
       <c r="H295" s="8"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="59"/>
       <c r="B296" s="66"/>
       <c r="C296" s="64"/>
@@ -11305,7 +11305,7 @@
       <c r="G296" s="37"/>
       <c r="H296" s="8"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="59"/>
       <c r="B297" s="66"/>
       <c r="C297" s="64"/>
@@ -11313,7 +11313,7 @@
       <c r="G297" s="37"/>
       <c r="H297" s="8"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="57"/>
       <c r="B298" s="66"/>
       <c r="C298" s="64"/>
@@ -11321,7 +11321,7 @@
       <c r="G298" s="37"/>
       <c r="H298" s="8"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="58"/>
       <c r="B299" s="66"/>
       <c r="C299" s="64"/>
@@ -11329,7 +11329,7 @@
       <c r="G299" s="37"/>
       <c r="H299" s="8"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="59"/>
       <c r="B300" s="66"/>
       <c r="C300" s="64"/>
@@ -11337,7 +11337,7 @@
       <c r="G300" s="37"/>
       <c r="H300" s="8"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="59"/>
       <c r="B301" s="66"/>
       <c r="C301" s="64"/>
@@ -11345,7 +11345,7 @@
       <c r="G301" s="37"/>
       <c r="H301" s="8"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="59"/>
       <c r="B302" s="66"/>
       <c r="C302" s="64"/>
@@ -11353,7 +11353,7 @@
       <c r="G302" s="37"/>
       <c r="H302" s="8"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="57"/>
       <c r="B303" s="66"/>
       <c r="C303" s="64"/>
@@ -11361,7 +11361,7 @@
       <c r="G303" s="37"/>
       <c r="H303" s="8"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="58"/>
       <c r="B304" s="66"/>
       <c r="C304" s="64"/>
@@ -11369,7 +11369,7 @@
       <c r="G304" s="37"/>
       <c r="H304" s="8"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="59"/>
       <c r="B305" s="66"/>
       <c r="C305" s="64"/>
@@ -11377,7 +11377,7 @@
       <c r="G305" s="37"/>
       <c r="H305" s="8"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="59"/>
       <c r="B306" s="66"/>
       <c r="C306" s="64"/>
@@ -11385,7 +11385,7 @@
       <c r="G306" s="37"/>
       <c r="H306" s="8"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="59"/>
       <c r="B307" s="66"/>
       <c r="C307" s="64"/>
@@ -11393,7 +11393,7 @@
       <c r="G307" s="37"/>
       <c r="H307" s="8"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="57"/>
       <c r="B308" s="66"/>
       <c r="C308" s="64"/>
@@ -11401,7 +11401,7 @@
       <c r="G308" s="37"/>
       <c r="H308" s="8"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="58"/>
       <c r="B309" s="66"/>
       <c r="C309" s="64"/>
@@ -11409,7 +11409,7 @@
       <c r="G309" s="37"/>
       <c r="H309" s="8"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="59"/>
       <c r="B310" s="66"/>
       <c r="C310" s="64"/>
@@ -11417,7 +11417,7 @@
       <c r="G310" s="37"/>
       <c r="H310" s="8"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="59"/>
       <c r="B311" s="66"/>
       <c r="C311" s="64"/>
@@ -11425,7 +11425,7 @@
       <c r="G311" s="37"/>
       <c r="H311" s="8"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="59"/>
       <c r="B312" s="66"/>
       <c r="C312" s="64"/>
@@ -11433,7 +11433,7 @@
       <c r="G312" s="37"/>
       <c r="H312" s="8"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="57"/>
       <c r="B313" s="66"/>
       <c r="C313" s="64"/>
@@ -11441,7 +11441,7 @@
       <c r="G313" s="37"/>
       <c r="H313" s="8"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="58"/>
       <c r="B314" s="66"/>
       <c r="C314" s="64"/>
@@ -11449,7 +11449,7 @@
       <c r="G314" s="37"/>
       <c r="H314" s="8"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="59"/>
       <c r="B315" s="66"/>
       <c r="C315" s="64"/>
@@ -11457,7 +11457,7 @@
       <c r="G315" s="37"/>
       <c r="H315" s="8"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="59"/>
       <c r="B316" s="66"/>
       <c r="C316" s="64"/>
@@ -11465,7 +11465,7 @@
       <c r="G316" s="37"/>
       <c r="H316" s="8"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="59"/>
       <c r="B317" s="66"/>
       <c r="C317" s="64"/>
@@ -11473,7 +11473,7 @@
       <c r="G317" s="37"/>
       <c r="H317" s="8"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="57"/>
       <c r="B318" s="66"/>
       <c r="C318" s="64"/>
@@ -11481,7 +11481,7 @@
       <c r="G318" s="37"/>
       <c r="H318" s="8"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="58"/>
       <c r="B319" s="66"/>
       <c r="C319" s="64"/>
@@ -11489,7 +11489,7 @@
       <c r="G319" s="37"/>
       <c r="H319" s="8"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="59"/>
       <c r="B320" s="66"/>
       <c r="C320" s="64"/>
@@ -11497,7 +11497,7 @@
       <c r="G320" s="37"/>
       <c r="H320" s="8"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="59"/>
       <c r="B321" s="66"/>
       <c r="C321" s="64"/>
@@ -11505,7 +11505,7 @@
       <c r="G321" s="37"/>
       <c r="H321" s="8"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="59"/>
       <c r="B322" s="66"/>
       <c r="C322" s="64"/>
@@ -11513,7 +11513,7 @@
       <c r="G322" s="37"/>
       <c r="H322" s="8"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="57"/>
       <c r="B323" s="66"/>
       <c r="C323" s="64"/>
@@ -11521,7 +11521,7 @@
       <c r="G323" s="37"/>
       <c r="H323" s="8"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="58"/>
       <c r="B324" s="66"/>
       <c r="C324" s="64"/>
@@ -11529,7 +11529,7 @@
       <c r="G324" s="37"/>
       <c r="H324" s="8"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="59"/>
       <c r="B325" s="66"/>
       <c r="C325" s="64"/>
@@ -11537,7 +11537,7 @@
       <c r="G325" s="37"/>
       <c r="H325" s="8"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="59"/>
       <c r="B326" s="66"/>
       <c r="C326" s="64"/>
@@ -11545,7 +11545,7 @@
       <c r="G326" s="37"/>
       <c r="H326" s="8"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="59"/>
       <c r="B327" s="66"/>
       <c r="C327" s="64"/>
@@ -11553,7 +11553,7 @@
       <c r="G327" s="37"/>
       <c r="H327" s="8"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="57"/>
       <c r="B328" s="66"/>
       <c r="C328" s="64"/>
@@ -11561,7 +11561,7 @@
       <c r="G328" s="37"/>
       <c r="H328" s="8"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="58"/>
       <c r="B329" s="66"/>
       <c r="C329" s="64"/>
@@ -11569,7 +11569,7 @@
       <c r="G329" s="37"/>
       <c r="H329" s="8"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="59"/>
       <c r="B330" s="66"/>
       <c r="C330" s="64"/>
@@ -11577,7 +11577,7 @@
       <c r="G330" s="37"/>
       <c r="H330" s="8"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="59"/>
       <c r="B331" s="66"/>
       <c r="C331" s="64"/>
@@ -11585,7 +11585,7 @@
       <c r="G331" s="37"/>
       <c r="H331" s="8"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="59"/>
       <c r="B332" s="66"/>
       <c r="C332" s="64"/>
@@ -11593,7 +11593,7 @@
       <c r="G332" s="37"/>
       <c r="H332" s="8"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="57"/>
       <c r="B333" s="66"/>
       <c r="C333" s="64"/>
@@ -11601,7 +11601,7 @@
       <c r="G333" s="37"/>
       <c r="H333" s="8"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="58"/>
       <c r="B334" s="66"/>
       <c r="C334" s="64"/>
@@ -11609,7 +11609,7 @@
       <c r="G334" s="37"/>
       <c r="H334" s="8"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="59"/>
       <c r="B335" s="66"/>
       <c r="C335" s="64"/>
@@ -11617,7 +11617,7 @@
       <c r="G335" s="37"/>
       <c r="H335" s="8"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="59"/>
       <c r="B336" s="66"/>
       <c r="C336" s="64"/>
@@ -11625,7 +11625,7 @@
       <c r="G336" s="37"/>
       <c r="H336" s="8"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="59"/>
       <c r="B337" s="66"/>
       <c r="C337" s="64"/>
@@ -11633,7 +11633,7 @@
       <c r="G337" s="37"/>
       <c r="H337" s="8"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="57"/>
       <c r="B338" s="66"/>
       <c r="C338" s="64"/>
@@ -11641,7 +11641,7 @@
       <c r="G338" s="37"/>
       <c r="H338" s="8"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="58"/>
       <c r="B339" s="66"/>
       <c r="C339" s="64"/>
@@ -11649,7 +11649,7 @@
       <c r="G339" s="37"/>
       <c r="H339" s="8"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="59"/>
       <c r="B340" s="66"/>
       <c r="C340" s="64"/>
@@ -11657,7 +11657,7 @@
       <c r="G340" s="37"/>
       <c r="H340" s="8"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="59"/>
       <c r="B341" s="66"/>
       <c r="C341" s="64"/>
@@ -11665,7 +11665,7 @@
       <c r="G341" s="37"/>
       <c r="H341" s="8"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="59"/>
       <c r="B342" s="66"/>
       <c r="C342" s="64"/>
@@ -11673,7 +11673,7 @@
       <c r="G342" s="37"/>
       <c r="H342" s="8"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="57"/>
       <c r="B343" s="66"/>
       <c r="C343" s="64"/>
@@ -11681,7 +11681,7 @@
       <c r="G343" s="37"/>
       <c r="H343" s="8"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="58"/>
       <c r="B344" s="66"/>
       <c r="C344" s="64"/>
@@ -11689,7 +11689,7 @@
       <c r="G344" s="37"/>
       <c r="H344" s="8"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="59"/>
       <c r="B345" s="66"/>
       <c r="C345" s="64"/>
@@ -11697,7 +11697,7 @@
       <c r="G345" s="37"/>
       <c r="H345" s="8"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="59"/>
       <c r="B346" s="66"/>
       <c r="C346" s="64"/>
@@ -11717,14 +11717,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11746,7 +11746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>0</v>
       </c>
